--- a/docs/design-vi/ACSMS-SCR-015/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者販売店一括置換画面_v1.0.xlsx
+++ b/docs/design-vi/ACSMS-SCR-015/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者販売店一括置換画面_v1.0.xlsx
@@ -1543,7 +1543,7 @@
       <c r="Y2" s="23" t="n"/>
       <c r="Z2" s="21" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AA2" s="22" t="n"/>
@@ -1559,7 +1559,7 @@
       <c r="AG2" s="23" t="n"/>
       <c r="AH2" s="21" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="22" t="n"/>
@@ -2034,7 +2034,7 @@
       <c r="F4" s="11" t="n"/>
       <c r="G4" s="20" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="H4" s="10" t="n"/>
@@ -2807,7 +2807,7 @@
       <c r="Y2" s="23" t="n"/>
       <c r="Z2" s="21" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AA2" s="22" t="n"/>
@@ -2823,7 +2823,7 @@
       <c r="AG2" s="23" t="n"/>
       <c r="AH2" s="21" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="22" t="n"/>
@@ -6440,7 +6440,7 @@
       <c r="E2" s="11" t="n"/>
       <c r="F2" s="20" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="G2" s="10" t="n"/>
@@ -15187,7 +15187,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Gửi với dokusya_ids - new_hanbaiten_id - hanbaiten_tekiyo_date chưa thiết lập.</t>
+            <t>Gửi với dokusya_ids - new_hanbaiten_id - joho_henko_tekiyo_date chưa thiết lập.</t>
           </r>
         </is>
       </c>

--- a/docs/design-vi/ACSMS-SCR-015/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者販売店一括置換画面_v1.0.xlsx
+++ b/docs/design-vi/ACSMS-SCR-015/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者販売店一括置換画面_v1.0.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AH3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="3.33" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1365,20 +1365,80 @@
       <c r="AG2" s="10" t="n"/>
       <c r="AH2" s="11" t="n"/>
     </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="11" t="n"/>
+      <c r="O3" s="20" t="inlineStr">
+        <is>
+          <t>Bổ sung 4 ca kiểm thử (047〜050): đánh giá điều kiện có thể thay thế theo as-of ngày áp dụng và loại trừ bản điện tử (2 ca — đồng bộ với bản tiếng Nhật), cửa hàng giao báo đích là điều kiện tìm kiếm bắt buộc kèm loại trừ người đọc đang được cửa hàng đích giao, và cửa hàng giao báo (nguồn) là tùy chọn</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="11" t="n"/>
+      <c r="W3" s="19" t="inlineStr"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="11" t="n"/>
+      <c r="AC3" s="19" t="inlineStr"/>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="AC2:AH2"/>
     <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="O3:V3"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:V2"/>
     <mergeCell ref="W1:AB1"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="W3:AB3"/>
     <mergeCell ref="O1:V1"/>
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="W2:AB2"/>
+    <mergeCell ref="AC3:AH3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1543,7 +1603,7 @@
       <c r="Y2" s="23" t="n"/>
       <c r="Z2" s="21" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Kieu Thi Diem</t>
         </is>
       </c>
       <c r="AA2" s="22" t="n"/>
@@ -1559,7 +1619,7 @@
       <c r="AG2" s="23" t="n"/>
       <c r="AH2" s="21" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Kieu Thi Diem</t>
         </is>
       </c>
       <c r="AI2" s="22" t="n"/>
@@ -2034,7 +2094,7 @@
       <c r="F4" s="11" t="n"/>
       <c r="G4" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Kieu Thi Diem</t>
         </is>
       </c>
       <c r="H4" s="10" t="n"/>
@@ -2807,7 +2867,7 @@
       <c r="Y2" s="23" t="n"/>
       <c r="Z2" s="21" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Kieu Thi Diem</t>
         </is>
       </c>
       <c r="AA2" s="22" t="n"/>
@@ -2823,7 +2883,7 @@
       <c r="AG2" s="23" t="n"/>
       <c r="AH2" s="21" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Kieu Thi Diem</t>
         </is>
       </c>
       <c r="AI2" s="22" t="n"/>
@@ -6302,7 +6362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ64"/>
+  <dimension ref="A1:BQ69"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -6440,7 +6500,7 @@
       <c r="E2" s="11" t="n"/>
       <c r="F2" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Kieu Thi Diem</t>
         </is>
       </c>
       <c r="G2" s="10" t="n"/>
@@ -16020,8 +16080,450 @@
       <c r="BP64" s="10" t="n"/>
       <c r="BQ64" s="11" t="n"/>
     </row>
+    <row r="65" ht="22.5" customHeight="1">
+      <c r="A65" s="32" t="inlineStr">
+        <is>
+          <t>Logic nghiệp vụ — Đánh giá as-of・Điều kiện cửa hàng đích (Function — As-of / Destination)</t>
+        </is>
+      </c>
+      <c r="B65" s="10" t="n"/>
+      <c r="C65" s="10" t="n"/>
+      <c r="D65" s="10" t="n"/>
+      <c r="E65" s="10" t="n"/>
+      <c r="F65" s="10" t="n"/>
+      <c r="G65" s="10" t="n"/>
+      <c r="H65" s="10" t="n"/>
+      <c r="I65" s="10" t="n"/>
+      <c r="J65" s="10" t="n"/>
+      <c r="K65" s="10" t="n"/>
+      <c r="L65" s="10" t="n"/>
+      <c r="M65" s="10" t="n"/>
+      <c r="N65" s="10" t="n"/>
+      <c r="O65" s="10" t="n"/>
+      <c r="P65" s="10" t="n"/>
+      <c r="Q65" s="10" t="n"/>
+      <c r="R65" s="10" t="n"/>
+      <c r="S65" s="10" t="n"/>
+      <c r="T65" s="10" t="n"/>
+      <c r="U65" s="10" t="n"/>
+      <c r="V65" s="10" t="n"/>
+      <c r="W65" s="10" t="n"/>
+      <c r="X65" s="10" t="n"/>
+      <c r="Y65" s="10" t="n"/>
+      <c r="Z65" s="10" t="n"/>
+      <c r="AA65" s="10" t="n"/>
+      <c r="AB65" s="10" t="n"/>
+      <c r="AC65" s="10" t="n"/>
+      <c r="AD65" s="10" t="n"/>
+      <c r="AE65" s="10" t="n"/>
+      <c r="AF65" s="10" t="n"/>
+      <c r="AG65" s="10" t="n"/>
+      <c r="AH65" s="10" t="n"/>
+      <c r="AI65" s="10" t="n"/>
+      <c r="AJ65" s="10" t="n"/>
+      <c r="AK65" s="10" t="n"/>
+      <c r="AL65" s="10" t="n"/>
+      <c r="AM65" s="10" t="n"/>
+      <c r="AN65" s="10" t="n"/>
+      <c r="AO65" s="10" t="n"/>
+      <c r="AP65" s="10" t="n"/>
+      <c r="AQ65" s="10" t="n"/>
+      <c r="AR65" s="10" t="n"/>
+      <c r="AS65" s="10" t="n"/>
+      <c r="AT65" s="10" t="n"/>
+      <c r="AU65" s="10" t="n"/>
+      <c r="AV65" s="10" t="n"/>
+      <c r="AW65" s="10" t="n"/>
+      <c r="AX65" s="10" t="n"/>
+      <c r="AY65" s="10" t="n"/>
+      <c r="AZ65" s="10" t="n"/>
+      <c r="BA65" s="10" t="n"/>
+      <c r="BB65" s="10" t="n"/>
+      <c r="BC65" s="10" t="n"/>
+      <c r="BD65" s="10" t="n"/>
+      <c r="BE65" s="10" t="n"/>
+      <c r="BF65" s="10" t="n"/>
+      <c r="BG65" s="10" t="n"/>
+      <c r="BH65" s="10" t="n"/>
+      <c r="BI65" s="10" t="n"/>
+      <c r="BJ65" s="10" t="n"/>
+      <c r="BK65" s="10" t="n"/>
+      <c r="BL65" s="10" t="n"/>
+      <c r="BM65" s="10" t="n"/>
+      <c r="BN65" s="10" t="n"/>
+      <c r="BO65" s="10" t="n"/>
+      <c r="BP65" s="10" t="n"/>
+      <c r="BQ65" s="11" t="n"/>
+    </row>
+    <row r="66" ht="208" customHeight="1">
+      <c r="A66" s="44" t="n">
+        <v>47</v>
+      </c>
+      <c r="B66" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-015-047</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="n"/>
+      <c r="D66" s="11" t="n"/>
+      <c r="E66" s="46" t="inlineStr">
+        <is>
+          <t>Chỉ những người đọc có thể thay thế tại thời điểm ngày áp dụng mới hiển thị trong kết quả tìm kiếm</t>
+        </is>
+      </c>
+      <c r="F66" s="10" t="n"/>
+      <c r="G66" s="10" t="n"/>
+      <c r="H66" s="10" t="n"/>
+      <c r="I66" s="11" t="n"/>
+      <c r="J66" s="46" t="inlineStr">
+        <is>
+          <t>・role: CHUOKAI
+・Đã đăng nhập + đã xác thực MFA
+・Người đọc A: ngày bắt đầu đọc báo=2026-05-01, ngày dự kiến hủy=không có
+・Người đọc B: ngày bắt đầu đọc báo=2026-05-01, ngày dự kiến hủy=2026-08-01
+・Người đọc C: ngày bắt đầu đọc báo=2026-10-01 (bắt đầu ở tương lai), ngày dự kiến hủy=không có</t>
+        </is>
+      </c>
+      <c r="K66" s="10" t="n"/>
+      <c r="L66" s="10" t="n"/>
+      <c r="M66" s="10" t="n"/>
+      <c r="N66" s="10" t="n"/>
+      <c r="O66" s="10" t="n"/>
+      <c r="P66" s="11" t="n"/>
+      <c r="Q66" s="46" t="inlineStr"/>
+      <c r="R66" s="10" t="n"/>
+      <c r="S66" s="10" t="n"/>
+      <c r="T66" s="10" t="n"/>
+      <c r="U66" s="10" t="n"/>
+      <c r="V66" s="10" t="n"/>
+      <c r="W66" s="11" t="n"/>
+      <c r="X66" s="46" t="inlineStr"/>
+      <c r="Y66" s="10" t="n"/>
+      <c r="Z66" s="10" t="n"/>
+      <c r="AA66" s="10" t="n"/>
+      <c r="AB66" s="10" t="n"/>
+      <c r="AC66" s="10" t="n"/>
+      <c r="AD66" s="11" t="n"/>
+      <c r="AE66" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF66" s="11" t="n"/>
+      <c r="AG66" s="45" t="inlineStr"/>
+      <c r="AH66" s="10" t="n"/>
+      <c r="AI66" s="11" t="n"/>
+      <c r="AJ66" s="45" t="inlineStr"/>
+      <c r="AK66" s="10" t="n"/>
+      <c r="AL66" s="11" t="n"/>
+      <c r="AM66" s="45" t="inlineStr"/>
+      <c r="AN66" s="10" t="n"/>
+      <c r="AO66" s="11" t="n"/>
+      <c r="AP66" s="45" t="inlineStr"/>
+      <c r="AQ66" s="10" t="n"/>
+      <c r="AR66" s="11" t="n"/>
+      <c r="AS66" s="45" t="inlineStr"/>
+      <c r="AT66" s="10" t="n"/>
+      <c r="AU66" s="11" t="n"/>
+      <c r="AV66" s="45" t="inlineStr"/>
+      <c r="AW66" s="10" t="n"/>
+      <c r="AX66" s="11" t="n"/>
+      <c r="AY66" s="45" t="inlineStr"/>
+      <c r="AZ66" s="10" t="n"/>
+      <c r="BA66" s="11" t="n"/>
+      <c r="BB66" s="45" t="inlineStr"/>
+      <c r="BC66" s="10" t="n"/>
+      <c r="BD66" s="11" t="n"/>
+      <c r="BE66" s="45" t="inlineStr"/>
+      <c r="BF66" s="10" t="n"/>
+      <c r="BG66" s="11" t="n"/>
+      <c r="BH66" s="45" t="inlineStr"/>
+      <c r="BI66" s="10" t="n"/>
+      <c r="BJ66" s="11" t="n"/>
+      <c r="BK66" s="46" t="inlineStr"/>
+      <c r="BL66" s="10" t="n"/>
+      <c r="BM66" s="10" t="n"/>
+      <c r="BN66" s="10" t="n"/>
+      <c r="BO66" s="10" t="n"/>
+      <c r="BP66" s="10" t="n"/>
+      <c r="BQ66" s="11" t="n"/>
+    </row>
+    <row r="67" ht="112" customHeight="1">
+      <c r="A67" s="44" t="n">
+        <v>48</v>
+      </c>
+      <c r="B67" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-015-048</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="n"/>
+      <c r="D67" s="11" t="n"/>
+      <c r="E67" s="46" t="inlineStr">
+        <is>
+          <t>Khi chọn bản điện tử ở loại đăng ký thì hiển thị thông báo ngoài phạm vi và không tìm kiếm được</t>
+        </is>
+      </c>
+      <c r="F67" s="10" t="n"/>
+      <c r="G67" s="10" t="n"/>
+      <c r="H67" s="10" t="n"/>
+      <c r="I67" s="11" t="n"/>
+      <c r="J67" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN
+・Đã đăng nhập + đã xác thực MFA
+・Radio loại đăng ký hiển thị "紙版" (bản giấy) và "電子版" (bản điện tử) (không hiển thị 併読 - kết hợp)</t>
+        </is>
+      </c>
+      <c r="K67" s="10" t="n"/>
+      <c r="L67" s="10" t="n"/>
+      <c r="M67" s="10" t="n"/>
+      <c r="N67" s="10" t="n"/>
+      <c r="O67" s="10" t="n"/>
+      <c r="P67" s="11" t="n"/>
+      <c r="Q67" s="46" t="inlineStr"/>
+      <c r="R67" s="10" t="n"/>
+      <c r="S67" s="10" t="n"/>
+      <c r="T67" s="10" t="n"/>
+      <c r="U67" s="10" t="n"/>
+      <c r="V67" s="10" t="n"/>
+      <c r="W67" s="11" t="n"/>
+      <c r="X67" s="46" t="inlineStr"/>
+      <c r="Y67" s="10" t="n"/>
+      <c r="Z67" s="10" t="n"/>
+      <c r="AA67" s="10" t="n"/>
+      <c r="AB67" s="10" t="n"/>
+      <c r="AC67" s="10" t="n"/>
+      <c r="AD67" s="11" t="n"/>
+      <c r="AE67" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF67" s="11" t="n"/>
+      <c r="AG67" s="45" t="inlineStr"/>
+      <c r="AH67" s="10" t="n"/>
+      <c r="AI67" s="11" t="n"/>
+      <c r="AJ67" s="45" t="inlineStr"/>
+      <c r="AK67" s="10" t="n"/>
+      <c r="AL67" s="11" t="n"/>
+      <c r="AM67" s="45" t="inlineStr"/>
+      <c r="AN67" s="10" t="n"/>
+      <c r="AO67" s="11" t="n"/>
+      <c r="AP67" s="45" t="inlineStr"/>
+      <c r="AQ67" s="10" t="n"/>
+      <c r="AR67" s="11" t="n"/>
+      <c r="AS67" s="45" t="inlineStr"/>
+      <c r="AT67" s="10" t="n"/>
+      <c r="AU67" s="11" t="n"/>
+      <c r="AV67" s="45" t="inlineStr"/>
+      <c r="AW67" s="10" t="n"/>
+      <c r="AX67" s="11" t="n"/>
+      <c r="AY67" s="45" t="inlineStr"/>
+      <c r="AZ67" s="10" t="n"/>
+      <c r="BA67" s="11" t="n"/>
+      <c r="BB67" s="45" t="inlineStr"/>
+      <c r="BC67" s="10" t="n"/>
+      <c r="BD67" s="11" t="n"/>
+      <c r="BE67" s="45" t="inlineStr"/>
+      <c r="BF67" s="10" t="n"/>
+      <c r="BG67" s="11" t="n"/>
+      <c r="BH67" s="45" t="inlineStr"/>
+      <c r="BI67" s="10" t="n"/>
+      <c r="BJ67" s="11" t="n"/>
+      <c r="BK67" s="46" t="inlineStr"/>
+      <c r="BL67" s="10" t="n"/>
+      <c r="BM67" s="10" t="n"/>
+      <c r="BN67" s="10" t="n"/>
+      <c r="BO67" s="10" t="n"/>
+      <c r="BP67" s="10" t="n"/>
+      <c r="BQ67" s="11" t="n"/>
+    </row>
+    <row r="68" ht="304" customHeight="1">
+      <c r="A68" s="44" t="n">
+        <v>49</v>
+      </c>
+      <c r="B68" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-015-049</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="n"/>
+      <c r="D68" s="11" t="n"/>
+      <c r="E68" s="46" t="inlineStr">
+        <is>
+          <t>Cửa hàng giao báo đích là điều kiện tìm kiếm (bắt buộc) và loại trừ người đọc đang được cửa hàng đích giao</t>
+        </is>
+      </c>
+      <c r="F68" s="10" t="n"/>
+      <c r="G68" s="10" t="n"/>
+      <c r="H68" s="10" t="n"/>
+      <c r="I68" s="11" t="n"/>
+      <c r="J68" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN (có quyền `dokusya.replace_hanbaiten`)
+・Tồn tại người đọc loại đăng ký=bản giấy・đang đọc báo như sau (ngày áp dụng là 2030/09/01)
+・(a) 3 người có cửa hàng giao báo của lịch sử hiệu lực tại ngày áp dụng = cửa hàng A (nguồn thay thế)
+・(b) 2 người có cửa hàng giao báo của lịch sử hiệu lực tại ngày áp dụng = cửa hàng B (đích thay thế)
+・(c) 2 người có cửa hàng giao báo của lịch sử hiệu lực tại ngày áp dụng = cửa hàng C (không phải A cũng không phải B)</t>
+        </is>
+      </c>
+      <c r="K68" s="10" t="n"/>
+      <c r="L68" s="10" t="n"/>
+      <c r="M68" s="10" t="n"/>
+      <c r="N68" s="10" t="n"/>
+      <c r="O68" s="10" t="n"/>
+      <c r="P68" s="11" t="n"/>
+      <c r="Q68" s="46" t="inlineStr"/>
+      <c r="R68" s="10" t="n"/>
+      <c r="S68" s="10" t="n"/>
+      <c r="T68" s="10" t="n"/>
+      <c r="U68" s="10" t="n"/>
+      <c r="V68" s="10" t="n"/>
+      <c r="W68" s="11" t="n"/>
+      <c r="X68" s="46" t="inlineStr"/>
+      <c r="Y68" s="10" t="n"/>
+      <c r="Z68" s="10" t="n"/>
+      <c r="AA68" s="10" t="n"/>
+      <c r="AB68" s="10" t="n"/>
+      <c r="AC68" s="10" t="n"/>
+      <c r="AD68" s="11" t="n"/>
+      <c r="AE68" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF68" s="11" t="n"/>
+      <c r="AG68" s="45" t="inlineStr"/>
+      <c r="AH68" s="10" t="n"/>
+      <c r="AI68" s="11" t="n"/>
+      <c r="AJ68" s="45" t="inlineStr"/>
+      <c r="AK68" s="10" t="n"/>
+      <c r="AL68" s="11" t="n"/>
+      <c r="AM68" s="45" t="inlineStr"/>
+      <c r="AN68" s="10" t="n"/>
+      <c r="AO68" s="11" t="n"/>
+      <c r="AP68" s="45" t="inlineStr"/>
+      <c r="AQ68" s="10" t="n"/>
+      <c r="AR68" s="11" t="n"/>
+      <c r="AS68" s="45" t="inlineStr"/>
+      <c r="AT68" s="10" t="n"/>
+      <c r="AU68" s="11" t="n"/>
+      <c r="AV68" s="45" t="inlineStr"/>
+      <c r="AW68" s="10" t="n"/>
+      <c r="AX68" s="11" t="n"/>
+      <c r="AY68" s="45" t="inlineStr"/>
+      <c r="AZ68" s="10" t="n"/>
+      <c r="BA68" s="11" t="n"/>
+      <c r="BB68" s="45" t="inlineStr"/>
+      <c r="BC68" s="10" t="n"/>
+      <c r="BD68" s="11" t="n"/>
+      <c r="BE68" s="45" t="inlineStr"/>
+      <c r="BF68" s="10" t="n"/>
+      <c r="BG68" s="11" t="n"/>
+      <c r="BH68" s="45" t="inlineStr"/>
+      <c r="BI68" s="10" t="n"/>
+      <c r="BJ68" s="11" t="n"/>
+      <c r="BK68" s="46" t="inlineStr"/>
+      <c r="BL68" s="10" t="n"/>
+      <c r="BM68" s="10" t="n"/>
+      <c r="BN68" s="10" t="n"/>
+      <c r="BO68" s="10" t="n"/>
+      <c r="BP68" s="10" t="n"/>
+      <c r="BQ68" s="11" t="n"/>
+    </row>
+    <row r="69" ht="96" customHeight="1">
+      <c r="A69" s="44" t="n">
+        <v>50</v>
+      </c>
+      <c r="B69" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-015-050</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="n"/>
+      <c r="D69" s="11" t="n"/>
+      <c r="E69" s="46" t="inlineStr">
+        <is>
+          <t>Cửa hàng giao báo (nguồn thay thế) là tùy chọn, khi không chỉ định thì đối tượng là toàn bộ cửa hàng trừ cửa hàng đích</t>
+        </is>
+      </c>
+      <c r="F69" s="10" t="n"/>
+      <c r="G69" s="10" t="n"/>
+      <c r="H69" s="10" t="n"/>
+      <c r="I69" s="11" t="n"/>
+      <c r="J69" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN (có quyền `dokusya.replace_hanbaiten`)
+・Dữ liệu giống ACSMS-TC-015-049 (cửa hàng A 3 bản ghi・cửa hàng B 2 bản ghi・cửa hàng C 2 bản ghi)</t>
+        </is>
+      </c>
+      <c r="K69" s="10" t="n"/>
+      <c r="L69" s="10" t="n"/>
+      <c r="M69" s="10" t="n"/>
+      <c r="N69" s="10" t="n"/>
+      <c r="O69" s="10" t="n"/>
+      <c r="P69" s="11" t="n"/>
+      <c r="Q69" s="46" t="inlineStr"/>
+      <c r="R69" s="10" t="n"/>
+      <c r="S69" s="10" t="n"/>
+      <c r="T69" s="10" t="n"/>
+      <c r="U69" s="10" t="n"/>
+      <c r="V69" s="10" t="n"/>
+      <c r="W69" s="11" t="n"/>
+      <c r="X69" s="46" t="inlineStr"/>
+      <c r="Y69" s="10" t="n"/>
+      <c r="Z69" s="10" t="n"/>
+      <c r="AA69" s="10" t="n"/>
+      <c r="AB69" s="10" t="n"/>
+      <c r="AC69" s="10" t="n"/>
+      <c r="AD69" s="11" t="n"/>
+      <c r="AE69" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF69" s="11" t="n"/>
+      <c r="AG69" s="45" t="inlineStr"/>
+      <c r="AH69" s="10" t="n"/>
+      <c r="AI69" s="11" t="n"/>
+      <c r="AJ69" s="45" t="inlineStr"/>
+      <c r="AK69" s="10" t="n"/>
+      <c r="AL69" s="11" t="n"/>
+      <c r="AM69" s="45" t="inlineStr"/>
+      <c r="AN69" s="10" t="n"/>
+      <c r="AO69" s="11" t="n"/>
+      <c r="AP69" s="45" t="inlineStr"/>
+      <c r="AQ69" s="10" t="n"/>
+      <c r="AR69" s="11" t="n"/>
+      <c r="AS69" s="45" t="inlineStr"/>
+      <c r="AT69" s="10" t="n"/>
+      <c r="AU69" s="11" t="n"/>
+      <c r="AV69" s="45" t="inlineStr"/>
+      <c r="AW69" s="10" t="n"/>
+      <c r="AX69" s="11" t="n"/>
+      <c r="AY69" s="45" t="inlineStr"/>
+      <c r="AZ69" s="10" t="n"/>
+      <c r="BA69" s="11" t="n"/>
+      <c r="BB69" s="45" t="inlineStr"/>
+      <c r="BC69" s="10" t="n"/>
+      <c r="BD69" s="11" t="n"/>
+      <c r="BE69" s="45" t="inlineStr"/>
+      <c r="BF69" s="10" t="n"/>
+      <c r="BG69" s="11" t="n"/>
+      <c r="BH69" s="45" t="inlineStr"/>
+      <c r="BI69" s="10" t="n"/>
+      <c r="BJ69" s="11" t="n"/>
+      <c r="BK69" s="46" t="inlineStr"/>
+      <c r="BL69" s="10" t="n"/>
+      <c r="BM69" s="10" t="n"/>
+      <c r="BN69" s="10" t="n"/>
+      <c r="BO69" s="10" t="n"/>
+      <c r="BP69" s="10" t="n"/>
+      <c r="BQ69" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="855">
+  <mergeCells count="924">
     <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="J31:P31"/>
     <mergeCell ref="B60:D60"/>
@@ -16066,6 +16568,7 @@
     <mergeCell ref="Q38:W38"/>
     <mergeCell ref="AE34:AF34"/>
     <mergeCell ref="AJ51:AL51"/>
+    <mergeCell ref="X68:AD68"/>
     <mergeCell ref="AE36:AF36"/>
     <mergeCell ref="AS51:AU51"/>
     <mergeCell ref="Q15:W15"/>
@@ -16080,18 +16583,21 @@
     <mergeCell ref="AM49:AO49"/>
     <mergeCell ref="AE50:AF50"/>
     <mergeCell ref="AG52:AI52"/>
+    <mergeCell ref="X69:AD69"/>
     <mergeCell ref="BE22:BG22"/>
     <mergeCell ref="BH23:BJ23"/>
     <mergeCell ref="BB26:BD26"/>
     <mergeCell ref="AE31:AF31"/>
     <mergeCell ref="H7:J7"/>
     <mergeCell ref="AG45:AI45"/>
+    <mergeCell ref="AS67:AU67"/>
     <mergeCell ref="AJ33:AL33"/>
     <mergeCell ref="E20:I20"/>
     <mergeCell ref="J39:P39"/>
     <mergeCell ref="AG37:AI37"/>
     <mergeCell ref="X21:AD21"/>
     <mergeCell ref="AE62:AF62"/>
+    <mergeCell ref="B68:D68"/>
     <mergeCell ref="AF8:AH8"/>
     <mergeCell ref="BB27:BD27"/>
     <mergeCell ref="AY31:BA31"/>
@@ -16104,21 +16610,25 @@
     <mergeCell ref="AE64:AF64"/>
     <mergeCell ref="AS62:AU62"/>
     <mergeCell ref="AV63:AX63"/>
+    <mergeCell ref="AP66:AR66"/>
     <mergeCell ref="BH49:BJ49"/>
     <mergeCell ref="R3:V3"/>
     <mergeCell ref="AP53:AR53"/>
     <mergeCell ref="X16:AD16"/>
     <mergeCell ref="AP28:AR28"/>
+    <mergeCell ref="BK66:BQ66"/>
     <mergeCell ref="BK53:BQ53"/>
     <mergeCell ref="BH60:BJ60"/>
     <mergeCell ref="AC7:AE7"/>
     <mergeCell ref="AY26:BA26"/>
     <mergeCell ref="BE15:BG15"/>
     <mergeCell ref="AS64:AU64"/>
+    <mergeCell ref="AP68:AR68"/>
     <mergeCell ref="AG63:AI63"/>
     <mergeCell ref="BE33:BG33"/>
     <mergeCell ref="BB37:BD37"/>
     <mergeCell ref="AG50:AI50"/>
+    <mergeCell ref="AP67:AR67"/>
     <mergeCell ref="BK13:BQ13"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="AM58:AO58"/>
@@ -16183,24 +16693,32 @@
     <mergeCell ref="Q34:W34"/>
     <mergeCell ref="X24:AD24"/>
     <mergeCell ref="BB43:BD43"/>
+    <mergeCell ref="BK68:BQ68"/>
     <mergeCell ref="E21:I21"/>
     <mergeCell ref="BH50:BJ50"/>
     <mergeCell ref="Q36:W36"/>
     <mergeCell ref="BE54:BG54"/>
+    <mergeCell ref="AJ67:AL67"/>
     <mergeCell ref="Q30:W30"/>
+    <mergeCell ref="BK67:BQ67"/>
     <mergeCell ref="AE63:AF63"/>
     <mergeCell ref="X26:AD26"/>
     <mergeCell ref="W1:AH1"/>
     <mergeCell ref="AC8:AE8"/>
+    <mergeCell ref="AP69:AR69"/>
     <mergeCell ref="AP44:AR44"/>
     <mergeCell ref="E23:I23"/>
     <mergeCell ref="BE56:BG56"/>
+    <mergeCell ref="AJ69:AL69"/>
+    <mergeCell ref="BK69:BQ69"/>
     <mergeCell ref="BE43:BG43"/>
     <mergeCell ref="J33:P33"/>
     <mergeCell ref="AE58:AF58"/>
+    <mergeCell ref="AV68:AX68"/>
     <mergeCell ref="BB59:BD59"/>
     <mergeCell ref="AM63:AO63"/>
     <mergeCell ref="X27:AD27"/>
+    <mergeCell ref="AG66:AI66"/>
     <mergeCell ref="BB46:BD46"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="AY60:BA60"/>
@@ -16210,10 +16728,12 @@
     <mergeCell ref="Q62:W62"/>
     <mergeCell ref="E34:I34"/>
     <mergeCell ref="BB48:BD48"/>
+    <mergeCell ref="AG68:AI68"/>
     <mergeCell ref="AG43:AI43"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="E49:I49"/>
+    <mergeCell ref="J68:P68"/>
     <mergeCell ref="Q64:W64"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="AY45:BA45"/>
@@ -16274,10 +16794,12 @@
     <mergeCell ref="AY37:BA37"/>
     <mergeCell ref="AS35:AU35"/>
     <mergeCell ref="J49:P49"/>
+    <mergeCell ref="AE68:AF68"/>
     <mergeCell ref="J36:P36"/>
     <mergeCell ref="BB62:BD62"/>
     <mergeCell ref="AJ14:AL14"/>
     <mergeCell ref="AY17:BA17"/>
+    <mergeCell ref="AY66:BA66"/>
     <mergeCell ref="AV21:AX21"/>
     <mergeCell ref="AY53:BA53"/>
     <mergeCell ref="BK24:BQ24"/>
@@ -16287,6 +16809,7 @@
     <mergeCell ref="BH53:BJ53"/>
     <mergeCell ref="BB64:BD64"/>
     <mergeCell ref="A8:G8"/>
+    <mergeCell ref="AY68:BA68"/>
     <mergeCell ref="AV23:AX23"/>
     <mergeCell ref="BB51:BD51"/>
     <mergeCell ref="AP63:AR63"/>
@@ -16331,6 +16854,7 @@
     <mergeCell ref="AS54:AU54"/>
     <mergeCell ref="E32:I32"/>
     <mergeCell ref="J26:P26"/>
+    <mergeCell ref="BH66:BJ66"/>
     <mergeCell ref="AS41:AU41"/>
     <mergeCell ref="AE49:AF49"/>
     <mergeCell ref="AY13:BA13"/>
@@ -16345,6 +16869,7 @@
     <mergeCell ref="AP38:AR38"/>
     <mergeCell ref="X41:AD41"/>
     <mergeCell ref="AS43:AU43"/>
+    <mergeCell ref="BH68:BJ68"/>
     <mergeCell ref="AY63:BA63"/>
     <mergeCell ref="BK38:BQ38"/>
     <mergeCell ref="F4:AH4"/>
@@ -16356,16 +16881,21 @@
     <mergeCell ref="AS36:AU36"/>
     <mergeCell ref="J50:P50"/>
     <mergeCell ref="AM39:AO39"/>
+    <mergeCell ref="BH67:BJ67"/>
     <mergeCell ref="J42:P42"/>
     <mergeCell ref="BK63:BQ63"/>
     <mergeCell ref="AJ15:AL15"/>
+    <mergeCell ref="AY67:BA67"/>
     <mergeCell ref="Q13:W13"/>
     <mergeCell ref="AG19:AI19"/>
     <mergeCell ref="X36:AD36"/>
     <mergeCell ref="J52:P52"/>
     <mergeCell ref="J44:P44"/>
     <mergeCell ref="AV37:AX37"/>
+    <mergeCell ref="BE66:BG66"/>
+    <mergeCell ref="AY69:BA69"/>
     <mergeCell ref="E60:I60"/>
+    <mergeCell ref="X67:AD67"/>
     <mergeCell ref="J37:P37"/>
     <mergeCell ref="AV60:AX60"/>
     <mergeCell ref="Q33:W33"/>
@@ -16382,6 +16912,7 @@
     <mergeCell ref="AM42:AO42"/>
     <mergeCell ref="X62:AD62"/>
     <mergeCell ref="AE37:AF37"/>
+    <mergeCell ref="B66:D66"/>
     <mergeCell ref="BH16:BJ16"/>
     <mergeCell ref="BB19:BD19"/>
     <mergeCell ref="AM23:AO23"/>
@@ -16397,6 +16928,7 @@
     <mergeCell ref="AY38:BA38"/>
     <mergeCell ref="Q22:W22"/>
     <mergeCell ref="BB58:BD58"/>
+    <mergeCell ref="B67:D67"/>
     <mergeCell ref="B61:D61"/>
     <mergeCell ref="AV58:AX58"/>
     <mergeCell ref="BB20:BD20"/>
@@ -16406,6 +16938,7 @@
     <mergeCell ref="BK17:BQ17"/>
     <mergeCell ref="BK55:BQ55"/>
     <mergeCell ref="BB60:BD60"/>
+    <mergeCell ref="B69:D69"/>
     <mergeCell ref="AP30:AR30"/>
     <mergeCell ref="AP59:AR59"/>
     <mergeCell ref="AJ30:AL30"/>
@@ -16429,6 +16962,7 @@
     <mergeCell ref="AP56:AR56"/>
     <mergeCell ref="AG20:AI20"/>
     <mergeCell ref="B16:D16"/>
+    <mergeCell ref="BE68:BG68"/>
     <mergeCell ref="AP43:AR43"/>
     <mergeCell ref="AM53:AO53"/>
     <mergeCell ref="B10:D11"/>
@@ -16438,15 +16972,18 @@
     <mergeCell ref="AM46:AO46"/>
     <mergeCell ref="AG22:AI22"/>
     <mergeCell ref="AJ23:AL23"/>
+    <mergeCell ref="E66:I66"/>
     <mergeCell ref="E53:I53"/>
     <mergeCell ref="AM48:AO48"/>
     <mergeCell ref="Q49:W49"/>
+    <mergeCell ref="E68:I68"/>
     <mergeCell ref="BK43:BQ43"/>
     <mergeCell ref="AM44:AO44"/>
     <mergeCell ref="AF6:AH6"/>
     <mergeCell ref="E55:I55"/>
     <mergeCell ref="AE32:AF32"/>
     <mergeCell ref="AV48:AX48"/>
+    <mergeCell ref="E67:I67"/>
     <mergeCell ref="AY14:BA14"/>
     <mergeCell ref="J51:P51"/>
     <mergeCell ref="F2:Q2"/>
@@ -16459,6 +16996,7 @@
     <mergeCell ref="AJ34:AL34"/>
     <mergeCell ref="BK34:BQ34"/>
     <mergeCell ref="J58:P58"/>
+    <mergeCell ref="A65:BQ65"/>
     <mergeCell ref="AS32:AU32"/>
     <mergeCell ref="AM45:AO45"/>
     <mergeCell ref="AJ49:AL49"/>
@@ -16475,6 +17013,7 @@
     <mergeCell ref="BK61:BQ61"/>
     <mergeCell ref="AJ44:AL44"/>
     <mergeCell ref="Q54:W54"/>
+    <mergeCell ref="AV66:AX66"/>
     <mergeCell ref="AY27:BA27"/>
     <mergeCell ref="AJ31:AL31"/>
     <mergeCell ref="B62:D62"/>
@@ -16507,7 +17046,9 @@
     <mergeCell ref="AP51:AR51"/>
     <mergeCell ref="AG59:AI59"/>
     <mergeCell ref="BK64:BQ64"/>
+    <mergeCell ref="J66:P66"/>
     <mergeCell ref="BK51:BQ51"/>
+    <mergeCell ref="AM67:AO67"/>
     <mergeCell ref="X60:AD60"/>
     <mergeCell ref="AM61:AO61"/>
     <mergeCell ref="B17:D17"/>
@@ -16521,6 +17062,7 @@
     <mergeCell ref="BH51:BJ51"/>
     <mergeCell ref="Z8:AB8"/>
     <mergeCell ref="AM20:AO20"/>
+    <mergeCell ref="AM69:AO69"/>
     <mergeCell ref="AJ24:AL24"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="J61:P61"/>
@@ -16529,6 +17071,7 @@
     <mergeCell ref="AM35:AO35"/>
     <mergeCell ref="AJ26:AL26"/>
     <mergeCell ref="AS13:AU13"/>
+    <mergeCell ref="E69:I69"/>
     <mergeCell ref="AP17:AR17"/>
     <mergeCell ref="Q42:W42"/>
     <mergeCell ref="A12:BQ12"/>
@@ -16547,6 +17090,7 @@
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="BE24:BG24"/>
     <mergeCell ref="AM38:AO38"/>
+    <mergeCell ref="BH69:BJ69"/>
     <mergeCell ref="BB28:BD28"/>
     <mergeCell ref="AG41:AI41"/>
     <mergeCell ref="BH35:BJ35"/>
@@ -16567,11 +17111,14 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="AG49:AI49"/>
     <mergeCell ref="AE51:AF51"/>
+    <mergeCell ref="AV67:AX67"/>
     <mergeCell ref="BB23:BD23"/>
     <mergeCell ref="E24:I24"/>
     <mergeCell ref="AG36:AI36"/>
     <mergeCell ref="B13:D13"/>
+    <mergeCell ref="AE66:AF66"/>
     <mergeCell ref="Q45:W45"/>
+    <mergeCell ref="AV69:AX69"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="BB31:BD31"/>
     <mergeCell ref="Q32:W32"/>
@@ -16582,7 +17129,10 @@
     <mergeCell ref="BH13:BJ13"/>
     <mergeCell ref="A25:BQ25"/>
     <mergeCell ref="E19:I19"/>
+    <mergeCell ref="AS66:AU66"/>
     <mergeCell ref="BE52:BG52"/>
+    <mergeCell ref="J67:P67"/>
+    <mergeCell ref="AE67:AF67"/>
     <mergeCell ref="BK21:BQ21"/>
     <mergeCell ref="BB56:BD56"/>
     <mergeCell ref="AE61:AF61"/>
@@ -16590,8 +17140,10 @@
     <mergeCell ref="AF7:AH7"/>
     <mergeCell ref="BH15:BJ15"/>
     <mergeCell ref="AY30:BA30"/>
+    <mergeCell ref="AS68:AU68"/>
     <mergeCell ref="AJ32:AL32"/>
     <mergeCell ref="AJ63:AL63"/>
+    <mergeCell ref="J69:P69"/>
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="AY46:BA46"/>
     <mergeCell ref="Q58:W58"/>
@@ -16654,6 +17206,7 @@
     <mergeCell ref="X28:AD28"/>
     <mergeCell ref="AS30:AU30"/>
     <mergeCell ref="AG60:AI60"/>
+    <mergeCell ref="AE69:AF69"/>
     <mergeCell ref="N7:P7"/>
     <mergeCell ref="AS42:AU42"/>
     <mergeCell ref="BH54:BJ54"/>
@@ -16662,6 +17215,7 @@
     <mergeCell ref="X30:AD30"/>
     <mergeCell ref="BE45:BG45"/>
     <mergeCell ref="AJ58:AL58"/>
+    <mergeCell ref="AS69:AU69"/>
     <mergeCell ref="X42:AD42"/>
     <mergeCell ref="E22:I22"/>
     <mergeCell ref="BH56:BJ56"/>
@@ -16672,6 +17226,7 @@
     <mergeCell ref="BE59:BG59"/>
     <mergeCell ref="AY62:BA62"/>
     <mergeCell ref="BB63:BD63"/>
+    <mergeCell ref="AJ66:AL66"/>
     <mergeCell ref="BE46:BG46"/>
     <mergeCell ref="BB50:BD50"/>
     <mergeCell ref="X54:AD54"/>
@@ -16680,7 +17235,9 @@
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="AY64:BA64"/>
+    <mergeCell ref="AJ68:AL68"/>
     <mergeCell ref="AV19:AX19"/>
+    <mergeCell ref="Q66:W66"/>
     <mergeCell ref="AS23:AU23"/>
     <mergeCell ref="E38:I38"/>
     <mergeCell ref="AY51:BA51"/>
@@ -16690,6 +17247,7 @@
     <mergeCell ref="E13:I13"/>
     <mergeCell ref="X43:AD43"/>
     <mergeCell ref="B30:D30"/>
+    <mergeCell ref="Q68:W68"/>
     <mergeCell ref="BK15:BQ15"/>
     <mergeCell ref="AE17:AF17"/>
     <mergeCell ref="E15:I15"/>
@@ -16739,6 +17297,7 @@
     <mergeCell ref="Q10:W11"/>
     <mergeCell ref="AP49:AR49"/>
     <mergeCell ref="E28:I28"/>
+    <mergeCell ref="BE67:BG67"/>
     <mergeCell ref="AG13:AI13"/>
     <mergeCell ref="AV33:AX33"/>
     <mergeCell ref="BE61:BG61"/>
@@ -16751,6 +17310,7 @@
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="Q28:W28"/>
     <mergeCell ref="E30:I30"/>
+    <mergeCell ref="BE69:BG69"/>
     <mergeCell ref="AG15:AI15"/>
     <mergeCell ref="AJ16:AL16"/>
     <mergeCell ref="X32:AD32"/>
@@ -16759,10 +17319,12 @@
     <mergeCell ref="E46:I46"/>
     <mergeCell ref="BE62:BG62"/>
     <mergeCell ref="J15:P15"/>
+    <mergeCell ref="BB66:BD66"/>
     <mergeCell ref="AM41:AO41"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="AY21:BA21"/>
     <mergeCell ref="E61:I61"/>
+    <mergeCell ref="Q67:W67"/>
     <mergeCell ref="A29:BQ29"/>
     <mergeCell ref="AV35:AX35"/>
     <mergeCell ref="AJ11:AL11"/>
@@ -16775,6 +17337,9 @@
     <mergeCell ref="AS63:AU63"/>
     <mergeCell ref="E41:I41"/>
     <mergeCell ref="J35:P35"/>
+    <mergeCell ref="AM66:AO66"/>
+    <mergeCell ref="BB68:BD68"/>
+    <mergeCell ref="Q69:W69"/>
     <mergeCell ref="AE27:AF27"/>
     <mergeCell ref="AP54:AR54"/>
     <mergeCell ref="B39:D39"/>
@@ -16788,6 +17353,7 @@
     <mergeCell ref="AE20:AF20"/>
     <mergeCell ref="BK23:BQ23"/>
     <mergeCell ref="X50:AD50"/>
+    <mergeCell ref="AM68:AO68"/>
     <mergeCell ref="BH52:BJ52"/>
     <mergeCell ref="AS27:AU27"/>
     <mergeCell ref="AP31:AR31"/>
@@ -16809,6 +17375,7 @@
     <mergeCell ref="Q24:W24"/>
     <mergeCell ref="AG30:AI30"/>
     <mergeCell ref="BK49:BQ49"/>
+    <mergeCell ref="AG67:AI67"/>
     <mergeCell ref="B63:D63"/>
     <mergeCell ref="AM37:AO37"/>
     <mergeCell ref="AE38:AF38"/>
@@ -16818,6 +17385,7 @@
     <mergeCell ref="AV41:AX41"/>
     <mergeCell ref="AE13:AF13"/>
     <mergeCell ref="AS45:AU45"/>
+    <mergeCell ref="AG69:AI69"/>
     <mergeCell ref="X53:AD53"/>
     <mergeCell ref="Q19:W19"/>
     <mergeCell ref="AS38:AU38"/>
@@ -16838,12 +17406,14 @@
     <mergeCell ref="AM43:AO43"/>
     <mergeCell ref="J41:P41"/>
     <mergeCell ref="Q44:W44"/>
+    <mergeCell ref="BB67:BD67"/>
     <mergeCell ref="AV43:AX43"/>
     <mergeCell ref="AJ19:AL19"/>
     <mergeCell ref="E62:I62"/>
     <mergeCell ref="J56:P56"/>
     <mergeCell ref="AY58:BA58"/>
     <mergeCell ref="J43:P43"/>
+    <mergeCell ref="BB69:BD69"/>
     <mergeCell ref="AG16:AI16"/>
     <mergeCell ref="E64:I64"/>
     <mergeCell ref="E51:I51"/>
@@ -16856,6 +17426,7 @@
     <mergeCell ref="AP32:AR32"/>
     <mergeCell ref="BK45:BQ45"/>
     <mergeCell ref="BH64:BJ64"/>
+    <mergeCell ref="X66:AD66"/>
     <mergeCell ref="BE19:BG19"/>
     <mergeCell ref="BK32:BQ32"/>
     <mergeCell ref="AM33:AO33"/>
@@ -16879,13 +17450,13 @@
     <mergeCell ref="BE60:BG60"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE17 AE19:AE24 AE26:AE28 AE30:AE39 AE41:AE46 AE48:AE56 AE58:AE64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE17 AE19:AE24 AE26:AE28 AE30:AE39 AE41:AE46 AE48:AE56 AE58:AE64 AE66:AE69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG17 AG19:AG24 AG26:AG28 AG30:AG39 AG41:AG46 AG48:AG56 AG58:AG64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG17 AG19:AG24 AG26:AG28 AG30:AG39 AG41:AG46 AG48:AG56 AG58:AG64 AG66:AG69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV17 AV19:AV24 AV26:AV28 AV30:AV39 AV41:AV46 AV48:AV56 AV58:AV64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV17 AV19:AV24 AV26:AV28 AV30:AV39 AV41:AV46 AV48:AV56 AV58:AV64 AV66:AV69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
